--- a/docs/verification/files/rocscience_gw/gw020.xlsx
+++ b/docs/verification/files/rocscience_gw/gw020.xlsx
@@ -6864,20 +6864,20 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>vg</t>
+          <t>gard</t>
         </is>
       </c>
       <c r="AK11" s="3">
-        <v>0.001</v>
+        <v>0.0</v>
       </c>
       <c r="AL11" s="3">
-        <v>-0.4</v>
+        <v>-10.1936799185</v>
       </c>
       <c r="AM11" s="3">
-        <v>1.7745</v>
+        <v>146.88069</v>
       </c>
       <c r="AN11" s="3">
-        <v>2.3276</v>
+        <v>4.45352</v>
       </c>
       <c r="AO11" s="3">
         <v>0.01962</v>
@@ -6994,20 +6994,20 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>vg</t>
+          <t>gard</t>
         </is>
       </c>
       <c r="AK12" s="3">
-        <v>0.001</v>
+        <v>0.0</v>
       </c>
       <c r="AL12" s="3">
-        <v>-0.4</v>
+        <v>-10.1936799185</v>
       </c>
       <c r="AM12" s="18">
-        <v>1.6722</v>
+        <v>115.81091</v>
       </c>
       <c r="AN12" s="19">
-        <v>2.1965</v>
+        <v>4.18902</v>
       </c>
       <c r="AO12" s="19">
         <v>0.01962</v>
@@ -8404,9 +8404,7 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="3">
-        <v>0</v>
-      </c>
+      <c r="B2" s="3"/>
       <c r="D2" s="24" t="s">
         <v>147</v>
       </c>
